--- a/artfynd/A 17341-2023 artfynd.xlsx
+++ b/artfynd/A 17341-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,131 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>JPN0072b Häckfågelinventering Hakerud Rölanda 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122291352</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58050</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hakerud, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>338408</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6490384</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vänersborg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Frändefors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>03:58</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>03:58</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>JPN0072b Häckfågelinventering Hakerud Rölanda 2024</t>
         </is>

--- a/artfynd/A 17341-2023 artfynd.xlsx
+++ b/artfynd/A 17341-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122286526</v>
       </c>
       <c r="B2" t="n">
-        <v>58050</v>
+        <v>58052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>122291352</v>
       </c>
       <c r="B3" t="n">
-        <v>58050</v>
+        <v>58052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 17341-2023 artfynd.xlsx
+++ b/artfynd/A 17341-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122286526</v>
       </c>
       <c r="B2" t="n">
-        <v>58052</v>
+        <v>58057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>122291352</v>
       </c>
       <c r="B3" t="n">
-        <v>58052</v>
+        <v>58057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 17341-2023 artfynd.xlsx
+++ b/artfynd/A 17341-2023 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>103044</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Spinus spinus</t>
@@ -817,11 +812,6 @@
       </c>
       <c r="E3" t="n">
         <v>103044</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 17341-2023 artfynd.xlsx
+++ b/artfynd/A 17341-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122286526</v>
       </c>
       <c r="B2" t="n">
-        <v>58057</v>
+        <v>58061</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>103044</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -798,7 +803,7 @@
         <v>122291352</v>
       </c>
       <c r="B3" t="n">
-        <v>58057</v>
+        <v>58061</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,6 +817,11 @@
       </c>
       <c r="E3" t="n">
         <v>103044</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 17341-2023 artfynd.xlsx
+++ b/artfynd/A 17341-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122286526</v>
       </c>
       <c r="B2" t="n">
-        <v>58061</v>
+        <v>58062</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>122291352</v>
       </c>
       <c r="B3" t="n">
-        <v>58061</v>
+        <v>58062</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
